--- a/output/yearly_surface_area_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_4_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626180777</v>
+        <v>10.84497625324618</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890716965769</v>
+        <v>37.78907166674425</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.926990816987241</v>
+        <v>6.059346830611313</v>
       </c>
       <c r="C2" t="n">
-        <v>5.457535487908019</v>
+        <v>8.021860491400687</v>
       </c>
       <c r="D2" t="n">
-        <v>24.5319116337193</v>
+        <v>22.04907168967911</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.65749322440488</v>
+        <v>17.49474408967816</v>
       </c>
       <c r="C3" t="n">
-        <v>36.52592333650258</v>
+        <v>32.79528206036471</v>
       </c>
       <c r="D3" t="n">
-        <v>82.07410807503335</v>
+        <v>69.1935781953152</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.48937768726719</v>
+        <v>35.69732827411827</v>
       </c>
       <c r="C4" t="n">
-        <v>83.5830542964607</v>
+        <v>66.36614480708438</v>
       </c>
       <c r="D4" t="n">
-        <v>114.3667353108237</v>
+        <v>82.1025787584565</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.20319038371264</v>
+        <v>45.9703362513569</v>
       </c>
       <c r="C5" t="n">
-        <v>130.0570271200962</v>
+        <v>115.2817241711817</v>
       </c>
       <c r="D5" t="n">
-        <v>85.85383673638358</v>
+        <v>57.13771638716437</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.16486116551801</v>
+        <v>44.39757642915352</v>
       </c>
       <c r="C6" t="n">
-        <v>136.4128617573901</v>
+        <v>157.9474976500439</v>
       </c>
       <c r="D6" t="n">
-        <v>55.42653013866219</v>
+        <v>41.37870223859457</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.87101550231194</v>
+        <v>31.62013005838127</v>
       </c>
       <c r="C7" t="n">
-        <v>105.7597531876919</v>
+        <v>159.1786092711693</v>
       </c>
       <c r="D7" t="n">
-        <v>40.90255460203486</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>16.85660808191773</v>
       </c>
       <c r="C8" t="n">
-        <v>63.83814446864884</v>
+        <v>105.8962161185822</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>53.69374544066654</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
         <v>34.87658719336794</v>
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
         <v>32.26022956155019</v>
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.663712514381428</v>
+        <v>7.648211876108843</v>
       </c>
       <c r="C21" t="n">
-        <v>93.88047830117247</v>
+        <v>92.73456899781972</v>
       </c>
       <c r="D21" t="n">
-        <v>7.663712514381428</v>
+        <v>7.648211876108843</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.867505117655686</v>
+        <v>6.909540342489052</v>
       </c>
       <c r="C2" t="n">
-        <v>10.56949578392116</v>
+        <v>7.727336180126644</v>
       </c>
       <c r="D2" t="n">
-        <v>25.91519414900306</v>
+        <v>23.0681258066873</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.77392029058275</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="C3" t="n">
-        <v>28.71121161069797</v>
+        <v>31.76935570942678</v>
       </c>
       <c r="D3" t="n">
-        <v>81.88266727270522</v>
+        <v>69.90534528089414</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.38803668955152</v>
+        <v>34.05093737409637</v>
       </c>
       <c r="C4" t="n">
-        <v>86.27598824920969</v>
+        <v>73.69194617617408</v>
       </c>
       <c r="D4" t="n">
-        <v>124.9980812001124</v>
+        <v>93.83151858109315</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.70664702954201</v>
+        <v>49.55371537185777</v>
       </c>
       <c r="C5" t="n">
-        <v>141.1753198706914</v>
+        <v>117.2206758870692</v>
       </c>
       <c r="D5" t="n">
-        <v>103.8198197241002</v>
+        <v>70.85764055401356</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.58374864006191</v>
+        <v>52.00513938936205</v>
       </c>
       <c r="C6" t="n">
-        <v>167.0041202217207</v>
+        <v>168.3324248655666</v>
       </c>
       <c r="D6" t="n">
-        <v>66.41523219229674</v>
+        <v>47.93972214607601</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.91389360612931</v>
+        <v>40.96244121199391</v>
       </c>
       <c r="C7" t="n">
-        <v>146.5425345698086</v>
+        <v>191.7569250888955</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>40.60312155223958</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.52696183746906</v>
+        <v>24.45042657426681</v>
       </c>
       <c r="C8" t="n">
-        <v>98.96998606512095</v>
+        <v>152.4605097310084</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>12.09218647320796</v>
       </c>
       <c r="C9" t="n">
-        <v>56.35624521458389</v>
+        <v>88.63905497333174</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>37.01188845010476</v>
+        <v>45.98015372839937</v>
       </c>
       <c r="D10" t="n">
         <v>35.16129402759952</v>
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1287,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
         <v>20.25247339090745</v>
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.836868707142244</v>
+        <v>7.819188609526363</v>
       </c>
       <c r="C21" t="n">
-        <v>101.8792931928492</v>
+        <v>100.6720533476519</v>
       </c>
       <c r="D21" t="n">
-        <v>8.816477295535025</v>
+        <v>8.796587185717158</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.980807014271569</v>
+        <v>7.118652603493622</v>
       </c>
       <c r="C2" t="n">
-        <v>19.0223435174862</v>
+        <v>9.986337647598555</v>
       </c>
       <c r="D2" t="n">
-        <v>25.21618978357932</v>
+        <v>27.33578307704819</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.59367962362884</v>
+        <v>20.10619298297468</v>
       </c>
       <c r="C3" t="n">
-        <v>34.03719290623692</v>
+        <v>30.98395754602934</v>
       </c>
       <c r="D3" t="n">
-        <v>82.36372364778616</v>
+        <v>70.8821842466197</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.1162725019244</v>
+        <v>33.70634392990574</v>
       </c>
       <c r="C4" t="n">
-        <v>78.73322063748145</v>
+        <v>75.12137083355744</v>
       </c>
       <c r="D4" t="n">
-        <v>133.8426462676719</v>
+        <v>103.6332876602933</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.89670517353839</v>
+        <v>49.72552122010096</v>
       </c>
       <c r="C5" t="n">
-        <v>148.4402528821178</v>
+        <v>123.5284048868549</v>
       </c>
       <c r="D5" t="n">
-        <v>118.0060740504666</v>
+        <v>82.73678777539996</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.13847715069036</v>
+        <v>57.72087452348698</v>
       </c>
       <c r="C6" t="n">
-        <v>189.3035375759827</v>
+        <v>174.6116831819292</v>
       </c>
       <c r="D6" t="n">
-        <v>78.85299385739957</v>
+        <v>56.47307319138928</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.95677170994669</v>
+        <v>49.28667999630262</v>
       </c>
       <c r="C7" t="n">
-        <v>184.9897381635222</v>
+        <v>214.6336100932547</v>
       </c>
       <c r="D7" t="n">
-        <v>53.23919625360028</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.78698611037422</v>
+        <v>32.62838495064274</v>
       </c>
       <c r="C8" t="n">
-        <v>139.1087409532518</v>
+        <v>193.600647277471</v>
       </c>
       <c r="D8" t="n">
-        <v>40.97324043674063</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>16.86249856814321</v>
       </c>
       <c r="C9" t="n">
-        <v>82.98124295375739</v>
+        <v>129.0203015444115</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>48.9695754878309</v>
+        <v>69.75317438673588</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1531,7 +1531,7 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>40.69246059332603</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1598,7 +1598,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
         <v>21.49242074137117</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.994047754526015</v>
+        <v>7.974375038775564</v>
       </c>
       <c r="C21" t="n">
-        <v>108.9189006554169</v>
+        <v>107.6540630234701</v>
       </c>
       <c r="D21" t="n">
-        <v>9.992559693157519</v>
+        <v>9.967968798469455</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.462444226429254</v>
+        <v>6.627778751370216</v>
       </c>
       <c r="C2" t="n">
-        <v>13.23886779176824</v>
+        <v>6.949791998363171</v>
       </c>
       <c r="D2" t="n">
-        <v>20.96325872878214</v>
+        <v>22.54878127114074</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.28995973011808</v>
+        <v>23.54721868635975</v>
       </c>
       <c r="C3" t="n">
-        <v>55.35584430395641</v>
+        <v>47.1386160194106</v>
       </c>
       <c r="D3" t="n">
-        <v>90.92947236733959</v>
+        <v>76.88557145808896</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.04121770804514</v>
+        <v>23.89181213055038</v>
       </c>
       <c r="C4" t="n">
-        <v>116.4215332558123</v>
+        <v>102.0379476408922</v>
       </c>
       <c r="D4" t="n">
-        <v>129.7841012583156</v>
+        <v>97.37955478424112</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.48326621686347</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="C5" t="n">
-        <v>113.0973355292326</v>
+        <v>104.3352372688298</v>
       </c>
       <c r="D5" t="n">
-        <v>78.83434065101889</v>
+        <v>55.98416283467437</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.29062268265284</v>
+        <v>30.59125846433062</v>
       </c>
       <c r="C6" t="n">
-        <v>121.8417623309589</v>
+        <v>141.3638154299067</v>
       </c>
       <c r="D6" t="n">
-        <v>35.05919226635785</v>
+        <v>28.73968229412113</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>21.61906619521901</v>
       </c>
       <c r="C7" t="n">
-        <v>97.79483406313751</v>
+        <v>136.122264436933</v>
       </c>
       <c r="D7" t="n">
-        <v>28.80545939030566</v>
+        <v>27.18852092141116</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>61.16779071309751</v>
+        <v>95.04790398665493</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>37.38593432542277</v>
+        <v>53.24999547834697</v>
       </c>
       <c r="D9" t="n">
         <v>27.17968519207294</v>
@@ -1828,7 +1828,7 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1845,7 +1845,7 @@
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>27.8983245115816</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1895,7 +1895,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
         <v>17.91689560250429</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.473423377625215</v>
+        <v>4.077198215737003</v>
       </c>
       <c r="C2" t="n">
-        <v>5.94644584462293</v>
+        <v>3.07483380970101</v>
       </c>
       <c r="D2" t="n">
-        <v>14.78315693054847</v>
+        <v>16.07120991852029</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.95754816900591</v>
+        <v>23.77792939685775</v>
       </c>
       <c r="C3" t="n">
-        <v>54.63916847985624</v>
+        <v>37.88073516836318</v>
       </c>
       <c r="D3" t="n">
-        <v>88.45055941411638</v>
+        <v>78.06857744170637</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.63128913602648</v>
+        <v>32.67256359733385</v>
       </c>
       <c r="C4" t="n">
-        <v>129.7585758180052</v>
+        <v>113.0904632953028</v>
       </c>
       <c r="D4" t="n">
-        <v>142.4319569321272</v>
+        <v>111.0484280704695</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>35.83379120500859</v>
       </c>
       <c r="C5" t="n">
-        <v>160.8348176482337</v>
+        <v>142.3288734231814</v>
       </c>
       <c r="D5" t="n">
-        <v>100.0155473701438</v>
+        <v>70.46494147231483</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.08056973167303</v>
+        <v>35.783722072092</v>
       </c>
       <c r="C6" t="n">
-        <v>150.6619479368283</v>
+        <v>160.000332099624</v>
       </c>
       <c r="D6" t="n">
-        <v>43.79380159104173</v>
+        <v>34.65667570761666</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.58859095865835</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>126.6601800634022</v>
+        <v>165.5864765367883</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>82.5306207575081</v>
+        <v>124.5052438525805</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>41.26874649571891</v>
+        <v>57.02187015806322</v>
       </c>
       <c r="D9" t="n">
         <v>28.39999758845172</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2192,7 +2192,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>15.05706454003333</v>
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.223077713042279</v>
+        <v>3.990804417763284</v>
       </c>
       <c r="C2" t="n">
-        <v>10.87776456305466</v>
+        <v>4.252931054797182</v>
       </c>
       <c r="D2" t="n">
-        <v>16.73585311429538</v>
+        <v>16.55324804130547</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.38398652554752</v>
+        <v>19.00172681569702</v>
       </c>
       <c r="C3" t="n">
-        <v>38.11635461738241</v>
+        <v>24.32770811123596</v>
       </c>
       <c r="D3" t="n">
-        <v>80.52785544084463</v>
+        <v>73.1303864893449</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.38352886165779</v>
+        <v>38.32644862609123</v>
       </c>
       <c r="C4" t="n">
-        <v>134.2000024320178</v>
+        <v>103.7226267013798</v>
       </c>
       <c r="D4" t="n">
-        <v>152.3868786531899</v>
+        <v>122.6752661318644</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.28186906877263</v>
+        <v>41.8469958935203</v>
       </c>
       <c r="C5" t="n">
-        <v>197.5030944018521</v>
+        <v>175.3646836710865</v>
       </c>
       <c r="D5" t="n">
-        <v>123.675667042492</v>
+        <v>90.2962450981004</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>41.78121879733577</v>
       </c>
       <c r="C6" t="n">
-        <v>198.0783985565407</v>
+        <v>190.1890740052134</v>
       </c>
       <c r="D6" t="n">
-        <v>60.49823877880121</v>
+        <v>45.8466360406218</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="C7" t="n">
-        <v>168.8802400845363</v>
+        <v>197.6258128648829</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>32.15910954801276</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>120.0824704449486</v>
+        <v>167.3143524962627</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>66.45155685735384</v>
+        <v>96.84842927624356</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>47.40368789955724</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.05273663858884</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.46605242207675</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.9546596791554</v>
+        <v>2.402336632291945</v>
       </c>
       <c r="C2" t="n">
-        <v>5.294565369003049</v>
+        <v>2.029272504678157</v>
       </c>
       <c r="D2" t="n">
-        <v>11.68476117594554</v>
+        <v>11.543389506534</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.01092239793373</v>
+        <v>18.55012287174348</v>
       </c>
       <c r="C3" t="n">
-        <v>42.28387362191012</v>
+        <v>22.61946710584651</v>
       </c>
       <c r="D3" t="n">
-        <v>79.05032514595318</v>
+        <v>72.49225048158448</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.76564970278805</v>
+        <v>42.34670547498192</v>
       </c>
       <c r="C4" t="n">
-        <v>133.4980528234813</v>
+        <v>98.69411496022759</v>
       </c>
       <c r="D4" t="n">
-        <v>160.6060704331442</v>
+        <v>131.1114241544573</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.1226460142354</v>
+        <v>43.95775345765094</v>
       </c>
       <c r="C5" t="n">
-        <v>239.8409641474958</v>
+        <v>209.7749407049373</v>
       </c>
       <c r="D5" t="n">
-        <v>129.9343086570654</v>
+        <v>95.62222639363934</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.47050349670826</v>
+        <v>34.41516577237194</v>
       </c>
       <c r="C6" t="n">
-        <v>230.7627431263256</v>
+        <v>227.3011007211513</v>
       </c>
       <c r="D6" t="n">
-        <v>58.64666260859173</v>
+        <v>45.28311285838414</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.665486074759095</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>168.3412605949048</v>
+        <v>212.1183724749743</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>84.28304040958866</v>
+        <v>120.5831617741145</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>11.82515109765283</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.18348900970292</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.607521902479529</v>
+        <v>3.426299487821368</v>
       </c>
       <c r="C2" t="n">
-        <v>3.98000519301657</v>
+        <v>3.431208226342602</v>
       </c>
       <c r="D2" t="n">
-        <v>15.87878736848791</v>
+        <v>14.15974713835175</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.10356653503143</v>
+        <v>13.48430471782994</v>
       </c>
       <c r="C3" t="n">
-        <v>31.67608967752334</v>
+        <v>15.2661768010379</v>
       </c>
       <c r="D3" t="n">
-        <v>71.22088720458486</v>
+        <v>66.30723994482958</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.84298678724529</v>
+        <v>39.47509344006</v>
       </c>
       <c r="C4" t="n">
-        <v>120.0844339403571</v>
+        <v>78.26099999173873</v>
       </c>
       <c r="D4" t="n">
-        <v>162.6225802176671</v>
+        <v>135.9357323731261</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.66952054322988</v>
+        <v>52.30260894374884</v>
       </c>
       <c r="C5" t="n">
-        <v>244.4306346648497</v>
+        <v>198.5830168765236</v>
       </c>
       <c r="D5" t="n">
-        <v>151.7291076913446</v>
+        <v>115.2326367859694</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.88309957439917</v>
+        <v>44.1560664939088</v>
       </c>
       <c r="C6" t="n">
-        <v>296.5339488246364</v>
+        <v>275.6433394259685</v>
       </c>
       <c r="D6" t="n">
-        <v>79.21525876026665</v>
+        <v>59.65295400544471</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.10949807898591</v>
+        <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>238.4085942469997</v>
+        <v>265.5971151684108</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>137.4397698560322</v>
+        <v>184.5882033524853</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>55.57968278052466</v>
+        <v>76.10311853780424</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.52062938288707</v>
+      </c>
+      <c r="D14" t="n">
         <v>13.82791641431633</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.806415775814131</v>
+        <v>2.429825568010856</v>
       </c>
       <c r="C2" t="n">
-        <v>3.955461500410399</v>
+        <v>2.1392282475538</v>
       </c>
       <c r="D2" t="n">
-        <v>12.53691818323177</v>
+        <v>10.25140952774519</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.2494460323367</v>
+        <v>12.83635123302705</v>
       </c>
       <c r="C3" t="n">
-        <v>24.93148294934775</v>
+        <v>14.68203691701105</v>
       </c>
       <c r="D3" t="n">
-        <v>68.3738188622691</v>
+        <v>63.87250563829748</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.58849314766712</v>
+        <v>35.18681946790993</v>
       </c>
       <c r="C4" t="n">
-        <v>106.5559505758361</v>
+        <v>62.9457358054885</v>
       </c>
       <c r="D4" t="n">
-        <v>162.0482578106828</v>
+        <v>137.6586995940793</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.14843349645307</v>
+        <v>56.74501730546565</v>
       </c>
       <c r="C5" t="n">
-        <v>244.185197738788</v>
+        <v>184.9858111727053</v>
       </c>
       <c r="D5" t="n">
-        <v>167.0198281849886</v>
+        <v>128.2653375598458</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.35732477327939</v>
+        <v>51.36111289537615</v>
       </c>
       <c r="C6" t="n">
-        <v>335.3365450872873</v>
+        <v>302.2094323028872</v>
       </c>
       <c r="D6" t="n">
-        <v>92.82031844571895</v>
+        <v>71.84920573530283</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.31289978021425</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>300.331348944663</v>
+        <v>317.6984658327891</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>40.8426679920758</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>179.0805987316607</v>
+        <v>230.8187027454676</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>61.34843229067891</v>
+        <v>85.86561770883451</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3400,7 +3400,7 @@
         <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.519164609097316</v>
+        <v>3.176935570942678</v>
       </c>
       <c r="C2" t="n">
-        <v>3.713951565165684</v>
+        <v>5.617560363700249</v>
       </c>
       <c r="D2" t="n">
-        <v>16.55717503212246</v>
+        <v>10.8640200951952</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.290859362364314</v>
+        <v>10.60287520586555</v>
       </c>
       <c r="C3" t="n">
-        <v>20.76396394482004</v>
+        <v>11.65334524940964</v>
       </c>
       <c r="D3" t="n">
-        <v>63.46998907955629</v>
+        <v>58.26672624704819</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.5171854181556</v>
+        <v>30.03068052520568</v>
       </c>
       <c r="C4" t="n">
-        <v>86.88859881665971</v>
+        <v>51.16574510223102</v>
       </c>
       <c r="D4" t="n">
-        <v>159.2276966563817</v>
+        <v>137.5565978328376</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.43037501402116</v>
+        <v>55.19876467127693</v>
       </c>
       <c r="C5" t="n">
-        <v>224.010282416516</v>
+        <v>155.3370305044516</v>
       </c>
       <c r="D5" t="n">
-        <v>178.3835578616455</v>
+        <v>142.6970288122739</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.03909964838319</v>
+        <v>60.82025202579416</v>
       </c>
       <c r="C6" t="n">
-        <v>356.3881611094517</v>
+        <v>300.116346197433</v>
       </c>
       <c r="D6" t="n">
-        <v>114.1939477148763</v>
+        <v>88.19137802019524</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.99078872223005</v>
+        <v>31.50035683846316</v>
       </c>
       <c r="C7" t="n">
-        <v>373.2133532648334</v>
+        <v>369.7998164971673</v>
       </c>
       <c r="D7" t="n">
-        <v>56.65273302126644</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.260024272905162</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>256.3539605329271</v>
+        <v>303.3354969196582</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>115.5968651842449</v>
+        <v>158.0859240763426</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>55.8025395093887</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3767,7 +3767,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.374667770123787</v>
+        <v>8.089601082993719</v>
       </c>
       <c r="C2" t="n">
-        <v>5.916993413495526</v>
+        <v>12.98655863177681</v>
       </c>
       <c r="D2" t="n">
-        <v>19.41111560836793</v>
+        <v>3.261365873507904</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.840776945462769</v>
+        <v>2.298271375641783</v>
       </c>
       <c r="C2" t="n">
-        <v>2.198133109808608</v>
+        <v>3.23485868549324</v>
       </c>
       <c r="D2" t="n">
-        <v>12.31798844518473</v>
+        <v>8.08272884906399</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.18210635137117</v>
+        <v>14.04390090925062</v>
       </c>
       <c r="C3" t="n">
-        <v>22.52129233542183</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="D3" t="n">
-        <v>70.26859193146545</v>
+        <v>62.53242002200059</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.14027641518283</v>
+        <v>41.84895938892878</v>
       </c>
       <c r="C4" t="n">
-        <v>125.8531834505114</v>
+        <v>77.6101012638231</v>
       </c>
       <c r="D4" t="n">
-        <v>162.8905973409265</v>
+        <v>140.6068879499324</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.15790681613028</v>
+        <v>35.26928627506667</v>
       </c>
       <c r="C5" t="n">
-        <v>316.5400035417779</v>
+        <v>245.1669454430348</v>
       </c>
       <c r="D5" t="n">
-        <v>163.2155558310322</v>
+        <v>129.0752794158494</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.14091400552181</v>
+        <v>19.56230475482195</v>
       </c>
       <c r="C6" t="n">
-        <v>305.188054837572</v>
+        <v>299.432068047573</v>
       </c>
       <c r="D6" t="n">
-        <v>87.66810649383169</v>
+        <v>70.80266268257573</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.790928796724434</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>180.2586959767568</v>
+        <v>213.3161046741554</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>85.20097451305944</v>
+        <v>116.4941825859265</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>42.59999638267758</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>18.93300447639974</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4375,7 +4375,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.527640485537042</v>
+        <v>7.020477833068941</v>
       </c>
       <c r="C2" t="n">
-        <v>5.980807014271569</v>
+        <v>8.459719967494765</v>
       </c>
       <c r="D2" t="n">
-        <v>22.53700029868978</v>
+        <v>12.94827047131118</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.297150759217294</v>
+        <v>17.17567608579795</v>
       </c>
       <c r="C3" t="n">
-        <v>14.90783888898781</v>
+        <v>32.72165098254619</v>
       </c>
       <c r="D3" t="n">
-        <v>19.44351328260808</v>
+        <v>5.87576000991716</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39690433947646</v>
+        <v>13.39782386394869</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13673448314147</v>
+        <v>70.14154846420193</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576106392879584</v>
+        <v>1.576214572229257</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.394302724208723</v>
+        <v>4.566108572451915</v>
       </c>
       <c r="C2" t="n">
-        <v>5.123741268464104</v>
+        <v>8.521570072862314</v>
       </c>
       <c r="D2" t="n">
-        <v>32.2749557771139</v>
+        <v>17.09419102634546</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.19531103988288</v>
+        <v>21.49045724596268</v>
       </c>
       <c r="C3" t="n">
-        <v>20.17000658375072</v>
+        <v>32.88854809226815</v>
       </c>
       <c r="D3" t="n">
-        <v>33.6739462556656</v>
+        <v>15.32999040181394</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.93765117301371</v>
+        <v>19.83326712119406</v>
       </c>
       <c r="C4" t="n">
-        <v>23.27920156310037</v>
+        <v>50.3999818929185</v>
       </c>
       <c r="D4" t="n">
-        <v>25.25742318715769</v>
+        <v>18.14858806070654</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43804399520462</v>
+        <v>15.43802841257033</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12803492061529</v>
+        <v>86.12794798591868</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250114525306237</v>
+        <v>3.250111244751648</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.950372835439918</v>
+        <v>4.771293842639499</v>
       </c>
       <c r="C2" t="n">
-        <v>11.98517597344506</v>
+        <v>7.086254929253477</v>
       </c>
       <c r="D2" t="n">
-        <v>28.6091098494563</v>
+        <v>27.32891084311846</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.08102739556275</v>
+        <v>18.4666743168825</v>
       </c>
       <c r="C3" t="n">
-        <v>20.2240027074843</v>
+        <v>33.0259927708627</v>
       </c>
       <c r="D3" t="n">
-        <v>51.6791991515521</v>
+        <v>25.44690049407733</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.59826956698058</v>
+        <v>31.80469862677967</v>
       </c>
       <c r="C4" t="n">
-        <v>38.79866927183395</v>
+        <v>68.89316339781567</v>
       </c>
       <c r="D4" t="n">
-        <v>36.43756604312036</v>
+        <v>21.76043786463055</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.940195505498956</v>
+        <v>16.81242943522663</v>
       </c>
       <c r="C5" t="n">
-        <v>26.87534340375644</v>
+        <v>54.46245389309182</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71045084717198</v>
+        <v>29.20699420134261</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
         <v>29.79113408536946</v>
@@ -5235,7 +5235,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.15780900513902</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5319,10 +5319,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72815628122631</v>
+        <v>16.72502726260976</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0417533154805</v>
+        <v>102.0226663019195</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182039070306578</v>
+        <v>4.18125681565244</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.809001166028377</v>
+        <v>6.624833508257476</v>
       </c>
       <c r="C2" t="n">
-        <v>7.517242171417827</v>
+        <v>7.055820750421827</v>
       </c>
       <c r="D2" t="n">
-        <v>22.98173200871359</v>
+        <v>22.19437034990764</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.34395585385165</v>
+        <v>17.27385085622263</v>
       </c>
       <c r="C3" t="n">
-        <v>35.38709599957628</v>
+        <v>29.85494768614551</v>
       </c>
       <c r="D3" t="n">
-        <v>61.9286451838888</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.43984833369835</v>
+        <v>33.98712377332033</v>
       </c>
       <c r="C4" t="n">
-        <v>45.39699559207676</v>
+        <v>76.4104055692335</v>
       </c>
       <c r="D4" t="n">
-        <v>53.18225488675397</v>
+        <v>29.18834099496192</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.62928458288898</v>
+        <v>31.75953823238432</v>
       </c>
       <c r="C5" t="n">
-        <v>51.05088062083415</v>
+        <v>92.50517743265571</v>
       </c>
       <c r="D5" t="n">
-        <v>37.06097583531709</v>
+        <v>30.48326621686347</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.660397409788615</v>
+        <v>14.16858286768997</v>
       </c>
       <c r="C6" t="n">
-        <v>27.89439752076462</v>
+        <v>50.55607977789376</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>37.51454327467913</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,7 +5546,7 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.73257338047992</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04875066559199</v>
+        <v>18.03795906290138</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7466114850525</v>
+        <v>117.6762091246423</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016250221863994</v>
+        <v>6.012653020967126</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.035784885709391</v>
+        <v>6.240970155896973</v>
       </c>
       <c r="C2" t="n">
-        <v>10.83849465488479</v>
+        <v>6.239988408192727</v>
       </c>
       <c r="D2" t="n">
-        <v>29.97962964458485</v>
+        <v>29.79702457159494</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.10695374650067</v>
+        <v>17.95616551067416</v>
       </c>
       <c r="C3" t="n">
-        <v>29.91385254840031</v>
+        <v>26.67899386290707</v>
       </c>
       <c r="D3" t="n">
-        <v>61.7421131200819</v>
+        <v>45.01804097823749</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.27920156310037</v>
+        <v>24.41508365691393</v>
       </c>
       <c r="C4" t="n">
-        <v>57.44500341859361</v>
+        <v>62.37141339850411</v>
       </c>
       <c r="D4" t="n">
-        <v>62.15444715586556</v>
+        <v>35.91429451675682</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.41406085148068</v>
+        <v>25.05911015089984</v>
       </c>
       <c r="C5" t="n">
-        <v>51.00179323562181</v>
+        <v>87.645526296634</v>
       </c>
       <c r="D5" t="n">
-        <v>37.92000507653306</v>
+        <v>27.51347941151687</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.94845039776043</v>
+        <v>15.33588088803943</v>
       </c>
       <c r="C6" t="n">
-        <v>37.15227837181205</v>
+        <v>66.65674212754145</v>
       </c>
       <c r="D6" t="n">
-        <v>32.28182801104362</v>
+        <v>29.78622534684823</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>19.82246789644735</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.05206970824214</v>
+        <v>7.043809126078618</v>
       </c>
       <c r="C21" t="n">
-        <v>66.99466222830033</v>
+        <v>66.03571055698704</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407543567651337</v>
+        <v>4.402380703799136</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.462043315801753</v>
+        <v>5.009858534771474</v>
       </c>
       <c r="C2" t="n">
-        <v>7.898160280665589</v>
+        <v>7.689048019661019</v>
       </c>
       <c r="D2" t="n">
-        <v>31.3796018708408</v>
+        <v>21.61317570899353</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.54659679155399</v>
+        <v>20.2240027074843</v>
       </c>
       <c r="C3" t="n">
-        <v>37.78746913645973</v>
+        <v>25.20637230653686</v>
       </c>
       <c r="D3" t="n">
-        <v>72.00628536798231</v>
+        <v>59.16993413495526</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.62227348023901</v>
+        <v>30.68157925312132</v>
       </c>
       <c r="C4" t="n">
-        <v>67.79556946446775</v>
+        <v>65.23026271327082</v>
       </c>
       <c r="D4" t="n">
-        <v>80.08606897393356</v>
+        <v>51.17850782238623</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.20070280448963</v>
+        <v>32.0295188510522</v>
       </c>
       <c r="C5" t="n">
-        <v>84.74937056910592</v>
+        <v>104.4088683466483</v>
       </c>
       <c r="D5" t="n">
-        <v>52.05717201768713</v>
+        <v>34.38571334124454</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.76356303419254</v>
+        <v>25.72080810356219</v>
       </c>
       <c r="C6" t="n">
-        <v>62.9938414429966</v>
+        <v>108.7599741718702</v>
       </c>
       <c r="D6" t="n">
-        <v>37.55479493055324</v>
+        <v>32.28182801104362</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>13.05528097107408</v>
       </c>
       <c r="C7" t="n">
-        <v>39.58504918293564</v>
+        <v>67.97130230352791</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>23.28214680621311</v>
+        <v>30.62561963397925</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
         <v>23.18593553119691</v>
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27057922870725</v>
+        <v>7.259515024325998</v>
       </c>
       <c r="C21" t="n">
-        <v>76.34108190142614</v>
+        <v>75.31746837738223</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452934421530438</v>
+        <v>5.444636268244498</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.658973693727862</v>
+        <v>4.904811530417065</v>
       </c>
       <c r="C2" t="n">
-        <v>10.08843940884022</v>
+        <v>9.579894098040375</v>
       </c>
       <c r="D2" t="n">
-        <v>26.09092698806323</v>
+        <v>27.84432838784804</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.22476347101029</v>
+        <v>18.57466656434965</v>
       </c>
       <c r="C3" t="n">
-        <v>33.55613653115598</v>
+        <v>27.93563092434299</v>
       </c>
       <c r="D3" t="n">
-        <v>80.40022823929253</v>
+        <v>62.43424525157591</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.40829353844221</v>
+        <v>35.60798923303181</v>
       </c>
       <c r="C4" t="n">
-        <v>83.34056261351174</v>
+        <v>64.03056701868123</v>
       </c>
       <c r="D4" t="n">
-        <v>98.20913159432968</v>
+        <v>67.84662034508857</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.64373306101221</v>
+        <v>39.39262663290327</v>
       </c>
       <c r="C5" t="n">
-        <v>107.5013736150258</v>
+        <v>112.3364810584413</v>
       </c>
       <c r="D5" t="n">
-        <v>69.06595099376312</v>
+        <v>45.01313223971626</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.62521872335175</v>
+        <v>35.38120551335081</v>
       </c>
       <c r="C6" t="n">
-        <v>101.6756827380252</v>
+        <v>139.9147558184385</v>
       </c>
       <c r="D6" t="n">
-        <v>44.92084795551706</v>
+        <v>35.66296710446964</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>22.15804568485051</v>
       </c>
       <c r="C7" t="n">
-        <v>66.71368349438775</v>
+        <v>115.7608170508541</v>
       </c>
       <c r="D7" t="n">
-        <v>37.00992495469625</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>39.13737222979909</v>
+        <v>61.66848204226339</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.84687272033327</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.474831552746084</v>
+        <v>7.461661171328011</v>
       </c>
       <c r="C21" t="n">
-        <v>85.02620891248671</v>
+        <v>83.94368817744012</v>
       </c>
       <c r="D21" t="n">
-        <v>6.540477608652823</v>
+        <v>6.528953524912009</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_4_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497625324618</v>
+        <v>10.84497650699067</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907166674425</v>
+        <v>37.78907255091111</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.059346830611313</v>
+        <v>5.233697011339745</v>
       </c>
       <c r="C2" t="n">
-        <v>8.021860491400687</v>
+        <v>8.605018627723293</v>
       </c>
       <c r="D2" t="n">
-        <v>22.04907168967911</v>
+        <v>28.55707722113122</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.49474408967816</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="C3" t="n">
-        <v>32.79528206036471</v>
+        <v>24.70568097737099</v>
       </c>
       <c r="D3" t="n">
-        <v>69.1935781953152</v>
+        <v>75.76637907524758</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.69732827411827</v>
+        <v>40.80241633620168</v>
       </c>
       <c r="C4" t="n">
-        <v>66.36614480708438</v>
+        <v>66.44272112801563</v>
       </c>
       <c r="D4" t="n">
-        <v>82.1025787584565</v>
+        <v>109.5041389316892</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.9703362513569</v>
+        <v>49.2837347531899</v>
       </c>
       <c r="C5" t="n">
-        <v>115.2817241711817</v>
+        <v>126.6945412330509</v>
       </c>
       <c r="D5" t="n">
-        <v>57.13771638716437</v>
+        <v>80.724204981694</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.39757642915352</v>
+        <v>44.23656980565704</v>
       </c>
       <c r="C6" t="n">
-        <v>157.9474976500439</v>
+        <v>143.8594180941022</v>
       </c>
       <c r="D6" t="n">
-        <v>41.37870223859457</v>
+        <v>51.52211951887262</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.62013005838127</v>
+        <v>30.30262463928205</v>
       </c>
       <c r="C7" t="n">
-        <v>159.1786092711693</v>
+        <v>111.6286409636793</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.85660808191773</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="C8" t="n">
-        <v>105.8962161185822</v>
+        <v>65.25676990128548</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>53.69374544066654</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
         <v>32.26022956155019</v>
@@ -954,7 +954,7 @@
         <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.648211876108843</v>
+        <v>7.664584622964162</v>
       </c>
       <c r="C21" t="n">
-        <v>92.73456899781972</v>
+        <v>92.93308855344046</v>
       </c>
       <c r="D21" t="n">
-        <v>7.648211876108843</v>
+        <v>7.664584622964162</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.909540342489052</v>
+        <v>7.041094534858124</v>
       </c>
       <c r="C2" t="n">
-        <v>7.727336180126644</v>
+        <v>7.789186285494193</v>
       </c>
       <c r="D2" t="n">
-        <v>23.0681258066873</v>
+        <v>28.1771408595877</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.63357142660446</v>
+        <v>18.48140053244621</v>
       </c>
       <c r="C3" t="n">
-        <v>31.76935570942678</v>
+        <v>28.85356502781376</v>
       </c>
       <c r="D3" t="n">
-        <v>69.90534528089414</v>
+        <v>79.37430188835462</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.05093737409637</v>
+        <v>38.7220929509027</v>
       </c>
       <c r="C4" t="n">
-        <v>73.69194617617408</v>
+        <v>63.405193731076</v>
       </c>
       <c r="D4" t="n">
-        <v>93.83151858109315</v>
+        <v>118.5529075217321</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.55371537185777</v>
+        <v>54.29064804484862</v>
       </c>
       <c r="C5" t="n">
-        <v>117.2206758870692</v>
+        <v>124.5346962837079</v>
       </c>
       <c r="D5" t="n">
-        <v>70.85764055401356</v>
+        <v>98.19931411728723</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.00513938936205</v>
+        <v>54.50074205355744</v>
       </c>
       <c r="C6" t="n">
-        <v>168.3324248655666</v>
+        <v>168.6946897684337</v>
       </c>
       <c r="D6" t="n">
-        <v>47.93972214607601</v>
+        <v>61.9472983902695</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.96244121199391</v>
+        <v>40.06414206260808</v>
       </c>
       <c r="C7" t="n">
-        <v>191.7569250888955</v>
+        <v>154.6272269142811</v>
       </c>
       <c r="D7" t="n">
-        <v>40.60312155223958</v>
+        <v>44.6155244194963</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.45042657426681</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="C8" t="n">
-        <v>152.4605097310084</v>
+        <v>103.2258623630309</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.09218647320796</v>
+        <v>11.09374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>88.63905497333174</v>
+        <v>56.02343274284421</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>45.98015372839937</v>
+        <v>35.73070769606267</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.819188609526363</v>
+        <v>7.838170652770653</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6720533476519</v>
+        <v>100.9164471544221</v>
       </c>
       <c r="D21" t="n">
-        <v>8.796587185717158</v>
+        <v>8.817941984366984</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.118652603493622</v>
+        <v>8.103345550853172</v>
       </c>
       <c r="C2" t="n">
-        <v>9.986337647598555</v>
+        <v>7.198174167537614</v>
       </c>
       <c r="D2" t="n">
-        <v>27.33578307704819</v>
+        <v>34.3660783871596</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.10619298297468</v>
+        <v>20.33690369347268</v>
       </c>
       <c r="C3" t="n">
-        <v>30.98395754602934</v>
+        <v>29.21681167838507</v>
       </c>
       <c r="D3" t="n">
-        <v>70.8821842466197</v>
+        <v>81.67159151629215</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.70634392990574</v>
+        <v>36.25888796094745</v>
       </c>
       <c r="C4" t="n">
-        <v>75.12137083355744</v>
+        <v>66.37890752723959</v>
       </c>
       <c r="D4" t="n">
-        <v>103.6332876602933</v>
+        <v>126.4530312978062</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.72552122010096</v>
+        <v>55.93507544946203</v>
       </c>
       <c r="C5" t="n">
-        <v>123.5284048868549</v>
+        <v>120.8531423927824</v>
       </c>
       <c r="D5" t="n">
-        <v>82.73678777539996</v>
+        <v>113.88273369263</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.72087452348698</v>
+        <v>61.70578845502478</v>
       </c>
       <c r="C6" t="n">
-        <v>174.6116831819292</v>
+        <v>179.5626368544459</v>
       </c>
       <c r="D6" t="n">
-        <v>56.47307319138928</v>
+        <v>73.82153687313468</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.28667999630262</v>
+        <v>49.88554609589318</v>
       </c>
       <c r="C7" t="n">
-        <v>214.6336100932547</v>
+        <v>190.7987393295506</v>
       </c>
       <c r="D7" t="n">
-        <v>43.6573386601514</v>
+        <v>50.66407202536089</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.62838495064274</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="C8" t="n">
-        <v>193.600647277471</v>
+        <v>146.034971006713</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.86249856814321</v>
+        <v>15.97499864350409</v>
       </c>
       <c r="C9" t="n">
-        <v>129.0203015444115</v>
+        <v>84.86718029361549</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>69.75317438673588</v>
+        <v>48.11545498513618</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>40.69246059332603</v>
+        <v>35.53926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1612,7 +1612,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>19.36104647545135</v>
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.974375038775564</v>
+        <v>7.996362343433392</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6540630234701</v>
+        <v>107.9508916363508</v>
       </c>
       <c r="D21" t="n">
-        <v>9.967968798469455</v>
+        <v>9.995452929291741</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.627778751370216</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C2" t="n">
-        <v>6.949791998363171</v>
+        <v>4.951935420220912</v>
       </c>
       <c r="D2" t="n">
-        <v>22.54878127114074</v>
+        <v>28.27629737771663</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.54721868635975</v>
+        <v>24.52896639060656</v>
       </c>
       <c r="C3" t="n">
-        <v>47.1386160194106</v>
+        <v>42.86310476741574</v>
       </c>
       <c r="D3" t="n">
-        <v>76.88557145808896</v>
+        <v>89.42248964132074</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.89181213055038</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="C4" t="n">
-        <v>102.0379476408922</v>
+        <v>96.0139437276338</v>
       </c>
       <c r="D4" t="n">
-        <v>97.37955478424112</v>
+        <v>123.4793175016426</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.5203927031756</v>
+        <v>34.7538687303371</v>
       </c>
       <c r="C5" t="n">
-        <v>104.3352372688298</v>
+        <v>107.2804803815702</v>
       </c>
       <c r="D5" t="n">
-        <v>55.98416283467437</v>
+        <v>74.71100029318228</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.59125846433062</v>
+        <v>30.95352336719769</v>
       </c>
       <c r="C6" t="n">
-        <v>141.3638154299067</v>
+        <v>125.6656696390002</v>
       </c>
       <c r="D6" t="n">
-        <v>28.73968229412113</v>
+        <v>33.36862271964485</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.61906619521901</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="C7" t="n">
-        <v>136.122264436933</v>
+        <v>102.645649469821</v>
       </c>
       <c r="D7" t="n">
-        <v>27.18852092141116</v>
+        <v>28.20659329071511</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>95.04790398665493</v>
+        <v>62.50296759087318</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>53.24999547834697</v>
+        <v>36.72030938194344</v>
       </c>
       <c r="D9" t="n">
         <v>27.17968519207294</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
         <v>16.53263133951629</v>
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.077198215737003</v>
+        <v>4.473824288252715</v>
       </c>
       <c r="C2" t="n">
-        <v>3.07483380970101</v>
+        <v>3.233876937788994</v>
       </c>
       <c r="D2" t="n">
-        <v>16.07120991852029</v>
+        <v>20.53423498202629</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.77792939685775</v>
+        <v>25.67270246605409</v>
       </c>
       <c r="C3" t="n">
-        <v>37.88073516836318</v>
+        <v>31.49446635223768</v>
       </c>
       <c r="D3" t="n">
-        <v>78.06857744170637</v>
+        <v>92.19592690581797</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.67256359733385</v>
+        <v>35.86324363613598</v>
       </c>
       <c r="C4" t="n">
-        <v>113.0904632953028</v>
+        <v>104.8074579145725</v>
       </c>
       <c r="D4" t="n">
-        <v>111.0484280704695</v>
+        <v>136.5993938211969</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.83379120500859</v>
+        <v>38.48451000647497</v>
       </c>
       <c r="C5" t="n">
-        <v>142.3288734231814</v>
+        <v>141.3716694115407</v>
       </c>
       <c r="D5" t="n">
-        <v>70.46494147231483</v>
+        <v>94.1741485298753</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.783722072092</v>
+        <v>36.95102009244145</v>
       </c>
       <c r="C6" t="n">
-        <v>160.000332099624</v>
+        <v>149.0116300459894</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>42.82776185006286</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="C7" t="n">
-        <v>165.5864765367883</v>
+        <v>133.966346478407</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46421209985527</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>124.5052438525805</v>
+        <v>83.94924619014475</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>57.02187015806322</v>
+        <v>41.71249645803847</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.990804417763284</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C2" t="n">
-        <v>4.252931054797182</v>
+        <v>7.347399818583129</v>
       </c>
       <c r="D2" t="n">
-        <v>16.55324804130547</v>
+        <v>25.4380647647391</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.00172681569702</v>
+        <v>20.42035224833366</v>
       </c>
       <c r="C3" t="n">
-        <v>24.32770811123596</v>
+        <v>21.71135047941821</v>
       </c>
       <c r="D3" t="n">
-        <v>73.1303864893449</v>
+        <v>87.42463306317848</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.32644862609123</v>
+        <v>42.25736643389546</v>
       </c>
       <c r="C4" t="n">
-        <v>103.7226267013798</v>
+        <v>91.62356799424208</v>
       </c>
       <c r="D4" t="n">
-        <v>122.6752661318644</v>
+        <v>149.272774935319</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.8469958935203</v>
+        <v>45.43037501402116</v>
       </c>
       <c r="C5" t="n">
-        <v>175.3646836710865</v>
+        <v>166.1607989437727</v>
       </c>
       <c r="D5" t="n">
-        <v>90.2962450981004</v>
+        <v>117.1715885018568</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.78121879733577</v>
+        <v>43.59254331167113</v>
       </c>
       <c r="C6" t="n">
-        <v>190.1890740052134</v>
+        <v>185.6003852355638</v>
       </c>
       <c r="D6" t="n">
-        <v>45.8466360406218</v>
+        <v>58.32464936159877</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>29.04500583014188</v>
       </c>
       <c r="C7" t="n">
-        <v>197.6258128648829</v>
+        <v>170.8564982131851</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>167.3143524962627</v>
+        <v>126.0073178400781</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>96.84842927624356</v>
+        <v>68.44843168779184</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>47.40368789955724</v>
+        <v>38.72012945549421</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.402336632291945</v>
+        <v>3.148464887519521</v>
       </c>
       <c r="C2" t="n">
-        <v>2.029272504678157</v>
+        <v>3.513675033499335</v>
       </c>
       <c r="D2" t="n">
-        <v>11.543389506534</v>
+        <v>17.73919926803562</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55012287174348</v>
+        <v>21.02412708644545</v>
       </c>
       <c r="C3" t="n">
-        <v>22.61946710584651</v>
+        <v>26.01140542401924</v>
       </c>
       <c r="D3" t="n">
-        <v>72.49225048158448</v>
+        <v>89.59920422808516</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.34670547498192</v>
+        <v>46.45630136495907</v>
       </c>
       <c r="C4" t="n">
-        <v>98.69411496022759</v>
+        <v>87.36081946240242</v>
       </c>
       <c r="D4" t="n">
-        <v>131.1114241544573</v>
+        <v>159.2149339362265</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.95775345765094</v>
+        <v>47.14843349645307</v>
       </c>
       <c r="C5" t="n">
-        <v>209.7749407049373</v>
+        <v>193.6988220478957</v>
       </c>
       <c r="D5" t="n">
-        <v>95.62222639363934</v>
+        <v>123.4547738090364</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.41516577237194</v>
+        <v>35.34095385747668</v>
       </c>
       <c r="C6" t="n">
-        <v>227.3011007211513</v>
+        <v>221.1828490282852</v>
       </c>
       <c r="D6" t="n">
-        <v>45.28311285838414</v>
+        <v>56.63407981488576</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>212.1183724749743</v>
+        <v>173.3118492215064</v>
       </c>
       <c r="D7" t="n">
-        <v>32.57831581772616</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>120.5831617741145</v>
+        <v>88.70581381722054</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.426299487821368</v>
+        <v>4.079161711145497</v>
       </c>
       <c r="C2" t="n">
-        <v>3.431208226342602</v>
+        <v>10.34369381194439</v>
       </c>
       <c r="D2" t="n">
-        <v>14.15974713835175</v>
+        <v>19.93536888243573</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.48430471782994</v>
+        <v>15.96321767105314</v>
       </c>
       <c r="C3" t="n">
-        <v>15.2661768010379</v>
+        <v>19.87057353395544</v>
       </c>
       <c r="D3" t="n">
-        <v>66.30723994482958</v>
+        <v>84.31249284071608</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.47509344006</v>
+        <v>43.87823189360694</v>
       </c>
       <c r="C4" t="n">
-        <v>78.26099999173873</v>
+        <v>76.44869372969913</v>
       </c>
       <c r="D4" t="n">
-        <v>135.9357323731261</v>
+        <v>165.6983957750724</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.30260894374884</v>
+        <v>56.69592992025331</v>
       </c>
       <c r="C5" t="n">
-        <v>198.5830168765236</v>
+        <v>180.1752474218959</v>
       </c>
       <c r="D5" t="n">
-        <v>115.2326367859694</v>
+        <v>146.0104273141069</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.1560664939088</v>
+        <v>46.28940425523712</v>
       </c>
       <c r="C6" t="n">
-        <v>275.6433394259685</v>
+        <v>261.1527433112856</v>
       </c>
       <c r="D6" t="n">
-        <v>59.65295400544471</v>
+        <v>75.47185476397357</v>
       </c>
     </row>
     <row r="7">
@@ -3030,10 +3030,10 @@
         <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>265.5971151684108</v>
+        <v>237.689954927491</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>41.14210104187108</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>184.5882033524853</v>
+        <v>144.2825513546325</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>76.10311853780424</v>
+        <v>58.02030757328223</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.429825568010856</v>
+        <v>2.891246989006857</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1392282475538</v>
+        <v>5.951354583144164</v>
       </c>
       <c r="D2" t="n">
-        <v>10.25140952774519</v>
+        <v>14.10771451002667</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.83635123302705</v>
+        <v>15.20236320026186</v>
       </c>
       <c r="C3" t="n">
-        <v>14.68203691701105</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D3" t="n">
-        <v>63.87250563829748</v>
+        <v>82.37844986334986</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.18681946790993</v>
+        <v>39.41127983928396</v>
       </c>
       <c r="C4" t="n">
-        <v>62.9457358054885</v>
+        <v>66.57034832956771</v>
       </c>
       <c r="D4" t="n">
-        <v>137.6586995940793</v>
+        <v>168.9273639743402</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.74501730546565</v>
+        <v>61.89919275276141</v>
       </c>
       <c r="C5" t="n">
-        <v>184.9858111727053</v>
+        <v>171.5604113171301</v>
       </c>
       <c r="D5" t="n">
-        <v>128.2653375598458</v>
+        <v>161.2029730373263</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.36111289537615</v>
+        <v>54.13847715069036</v>
       </c>
       <c r="C6" t="n">
-        <v>302.2094323028872</v>
+        <v>282.4056176128205</v>
       </c>
       <c r="D6" t="n">
-        <v>71.84920573530283</v>
+        <v>90.92849061963534</v>
       </c>
     </row>
     <row r="7">
@@ -3341,10 +3341,10 @@
         <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>317.6984658327891</v>
+        <v>289.3720993221558</v>
       </c>
       <c r="D7" t="n">
-        <v>40.8426679920758</v>
+        <v>46.11268966847268</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>230.8187027454676</v>
+        <v>186.5075201142878</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +3369,7 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>85.86561770883451</v>
+        <v>66.67343183851361</v>
       </c>
       <c r="D9" t="n">
         <v>31.94999728700819</v>
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3442,7 +3442,7 @@
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.176935570942678</v>
+        <v>3.806235849364884</v>
       </c>
       <c r="C2" t="n">
-        <v>5.617560363700249</v>
+        <v>6.555129421255953</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8640200951952</v>
+        <v>18.01114338211198</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.60287520586555</v>
+        <v>12.58109682992288</v>
       </c>
       <c r="C3" t="n">
-        <v>11.65334524940964</v>
+        <v>26.59063656952486</v>
       </c>
       <c r="D3" t="n">
-        <v>58.26672624704819</v>
+        <v>75.68293052038661</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.03068052520568</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="C4" t="n">
-        <v>51.16574510223102</v>
+        <v>69.31433316293754</v>
       </c>
       <c r="D4" t="n">
-        <v>137.5565978328376</v>
+        <v>170.3057377511027</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.19876467127693</v>
+        <v>61.33468782281949</v>
       </c>
       <c r="C5" t="n">
-        <v>155.3370305044516</v>
+        <v>150.8455347575224</v>
       </c>
       <c r="D5" t="n">
-        <v>142.6970288122739</v>
+        <v>178.2853830912208</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.82025202579416</v>
+        <v>64.12088780747193</v>
       </c>
       <c r="C6" t="n">
-        <v>300.116346197433</v>
+        <v>279.6685050133804</v>
       </c>
       <c r="D6" t="n">
-        <v>88.19137802019524</v>
+        <v>111.3763318036879</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.50035683846316</v>
+        <v>32.75797564760332</v>
       </c>
       <c r="C7" t="n">
-        <v>369.7998164971673</v>
+        <v>336.6226345798506</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>56.11375353163493</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>303.3354969196582</v>
+        <v>262.5291535926395</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>158.0859240763426</v>
+        <v>123.473427015417</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>55.8025395093887</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.089601082993719</v>
+        <v>6.23606141737574</v>
       </c>
       <c r="C2" t="n">
-        <v>12.98655863177681</v>
+        <v>4.185190463204153</v>
       </c>
       <c r="D2" t="n">
-        <v>3.261365873507904</v>
+        <v>9.447358157967058</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.298271375641783</v>
+        <v>2.752820562708056</v>
       </c>
       <c r="C2" t="n">
-        <v>3.23485868549324</v>
+        <v>3.774819922828986</v>
       </c>
       <c r="D2" t="n">
-        <v>8.08272884906399</v>
+        <v>13.39987441526472</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.04390090925062</v>
+        <v>16.50808764691012</v>
       </c>
       <c r="C3" t="n">
-        <v>16.35591675275186</v>
+        <v>30.31146036862027</v>
       </c>
       <c r="D3" t="n">
-        <v>62.53242002200059</v>
+        <v>82.09865176763952</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.84895938892878</v>
+        <v>46.97957289132261</v>
       </c>
       <c r="C4" t="n">
-        <v>77.6101012638231</v>
+        <v>98.01769079200155</v>
       </c>
       <c r="D4" t="n">
-        <v>140.6068879499324</v>
+        <v>174.2877064395278</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.26928627506667</v>
+        <v>37.25732537616646</v>
       </c>
       <c r="C5" t="n">
-        <v>245.1669454430348</v>
+        <v>232.3796815952201</v>
       </c>
       <c r="D5" t="n">
-        <v>129.0752794158494</v>
+        <v>161.6202158116312</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.56230475482195</v>
+        <v>20.32708621643021</v>
       </c>
       <c r="C6" t="n">
-        <v>299.432068047573</v>
+        <v>273.791763255759</v>
       </c>
       <c r="D6" t="n">
-        <v>70.80266268257573</v>
+        <v>86.70206675285282</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>213.3161046741554</v>
+        <v>184.6304185037679</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>116.4941825859265</v>
+        <v>90.95892479846698</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>42.59999638267758</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.020477833068941</v>
+        <v>6.563965150594174</v>
       </c>
       <c r="C2" t="n">
-        <v>8.459719967494765</v>
+        <v>9.026188392845174</v>
       </c>
       <c r="D2" t="n">
-        <v>12.94827047131118</v>
+        <v>26.77716863333175</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.17567608579795</v>
+        <v>13.24377653028947</v>
       </c>
       <c r="C3" t="n">
-        <v>32.72165098254619</v>
+        <v>10.54397034361075</v>
       </c>
       <c r="D3" t="n">
-        <v>5.87576000991716</v>
+        <v>11.06920536538279</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39782386394869</v>
+        <v>13.39859138514819</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14154846420193</v>
+        <v>70.14556666342288</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576214572229257</v>
+        <v>1.576304868840964</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.566108572451915</v>
+        <v>5.614615120587509</v>
       </c>
       <c r="C2" t="n">
-        <v>8.521570072862314</v>
+        <v>5.62345084992573</v>
       </c>
       <c r="D2" t="n">
-        <v>17.09419102634546</v>
+        <v>25.81211064005714</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.49045724596268</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="C3" t="n">
-        <v>32.88854809226815</v>
+        <v>25.96722677732814</v>
       </c>
       <c r="D3" t="n">
-        <v>15.32999040181394</v>
+        <v>30.88578277560466</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.83326712119406</v>
+        <v>15.39184050718149</v>
       </c>
       <c r="C4" t="n">
-        <v>50.3999818929185</v>
+        <v>16.61706164208151</v>
       </c>
       <c r="D4" t="n">
-        <v>18.14858806070654</v>
+        <v>20.86704745376596</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43802841257033</v>
+        <v>15.44018670261402</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12794798591868</v>
+        <v>86.13998897247821</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250111244751648</v>
+        <v>3.250565621602951</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.771293842639499</v>
+        <v>6.221335201812037</v>
       </c>
       <c r="C2" t="n">
-        <v>7.086254929253477</v>
+        <v>10.9877203059303</v>
       </c>
       <c r="D2" t="n">
-        <v>27.32891084311846</v>
+        <v>31.7340127920739</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4666743168825</v>
+        <v>19.22262004915255</v>
       </c>
       <c r="C3" t="n">
-        <v>33.0259927708627</v>
+        <v>23.48831382410494</v>
       </c>
       <c r="D3" t="n">
-        <v>25.44690049407733</v>
+        <v>44.36517875491336</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.80469862677967</v>
+        <v>27.47813649416398</v>
       </c>
       <c r="C4" t="n">
-        <v>68.89316339781567</v>
+        <v>45.09069030835175</v>
       </c>
       <c r="D4" t="n">
-        <v>21.76043786463055</v>
+        <v>31.63878326476196</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.81242943522663</v>
+        <v>13.35176877775663</v>
       </c>
       <c r="C5" t="n">
-        <v>54.46245389309182</v>
+        <v>19.8067599331794</v>
       </c>
       <c r="D5" t="n">
-        <v>29.20699420134261</v>
+        <v>30.16419821298325</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
         <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5319,10 +5319,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72502726260976</v>
+        <v>16.73166530651699</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0226663019195</v>
+        <v>102.0631583697536</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18125681565244</v>
+        <v>4.182916326629248</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.624833508257476</v>
+        <v>5.698063675448488</v>
       </c>
       <c r="C2" t="n">
-        <v>7.055820750421827</v>
+        <v>8.630544068033711</v>
       </c>
       <c r="D2" t="n">
-        <v>22.19437034990764</v>
+        <v>30.1003846122072</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.27385085622263</v>
+        <v>20.28781630826034</v>
       </c>
       <c r="C3" t="n">
-        <v>29.85494768614551</v>
+        <v>34.53297549688155</v>
       </c>
       <c r="D3" t="n">
-        <v>40.55599766243574</v>
+        <v>58.61524668205582</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.98712377332033</v>
+        <v>32.45559735469531</v>
       </c>
       <c r="C4" t="n">
-        <v>76.4104055692335</v>
+        <v>52.73555968132166</v>
       </c>
       <c r="D4" t="n">
-        <v>29.18834099496192</v>
+        <v>45.94579255875072</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.75953823238432</v>
+        <v>27.26804248545517</v>
       </c>
       <c r="C5" t="n">
-        <v>92.50517743265571</v>
+        <v>54.0697548113931</v>
       </c>
       <c r="D5" t="n">
-        <v>30.48326621686347</v>
+        <v>34.23845118560752</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.16858286768997</v>
+        <v>11.87423848286517</v>
       </c>
       <c r="C6" t="n">
-        <v>50.55607977789376</v>
+        <v>22.05790741901734</v>
       </c>
       <c r="D6" t="n">
-        <v>37.51454327467913</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>47.73257338047992</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03795906290138</v>
+        <v>18.05221403152856</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6762091246423</v>
+        <v>117.7692058247339</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012653020967126</v>
+        <v>6.017404677176185</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.240970155896973</v>
+        <v>7.456373813754525</v>
       </c>
       <c r="C2" t="n">
-        <v>6.239988408192727</v>
+        <v>8.241771977151974</v>
       </c>
       <c r="D2" t="n">
-        <v>29.79702457159494</v>
+        <v>27.25822500841269</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.95616551067416</v>
+        <v>17.8039946165159</v>
       </c>
       <c r="C3" t="n">
-        <v>26.67899386290707</v>
+        <v>31.84789552576653</v>
       </c>
       <c r="D3" t="n">
-        <v>45.01804097823749</v>
+        <v>64.40264939859075</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.41508365691393</v>
+        <v>26.06147455693583</v>
       </c>
       <c r="C4" t="n">
-        <v>62.37141339850411</v>
+        <v>59.15520791939156</v>
       </c>
       <c r="D4" t="n">
-        <v>35.91429451675682</v>
+        <v>55.83690067903733</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.05911015089984</v>
+        <v>23.12015843501239</v>
       </c>
       <c r="C5" t="n">
-        <v>87.645526296634</v>
+        <v>57.43224069843842</v>
       </c>
       <c r="D5" t="n">
-        <v>27.51347941151687</v>
+        <v>34.18936380039518</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.33588088803943</v>
+        <v>13.32329809433347</v>
       </c>
       <c r="C6" t="n">
-        <v>66.65674212754145</v>
+        <v>36.8302651248191</v>
       </c>
       <c r="D6" t="n">
-        <v>29.78622534684823</v>
+        <v>31.31578827006476</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.28809404570082</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>30.06307819944583</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.39687241888974</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.043809126078618</v>
+        <v>7.052547678293223</v>
       </c>
       <c r="C21" t="n">
-        <v>66.03571055698704</v>
+        <v>66.11763448399896</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402380703799136</v>
+        <v>4.407842298933264</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.009858534771474</v>
+        <v>6.560038159777187</v>
       </c>
       <c r="C2" t="n">
-        <v>7.689048019661019</v>
+        <v>4.309872421643497</v>
       </c>
       <c r="D2" t="n">
-        <v>21.61317570899353</v>
+        <v>24.34439782220816</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.2240027074843</v>
+        <v>22.78636421556847</v>
       </c>
       <c r="C3" t="n">
-        <v>25.20637230653686</v>
+        <v>32.05406254365836</v>
       </c>
       <c r="D3" t="n">
-        <v>59.16993413495526</v>
+        <v>71.73630474931444</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.68157925312132</v>
+        <v>31.60049510429634</v>
       </c>
       <c r="C4" t="n">
-        <v>65.23026271327082</v>
+        <v>71.99450439553134</v>
       </c>
       <c r="D4" t="n">
-        <v>51.17850782238623</v>
+        <v>76.62737181187205</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.0295188510522</v>
+        <v>32.22586839190156</v>
       </c>
       <c r="C5" t="n">
-        <v>104.4088683466483</v>
+        <v>88.11185645615124</v>
       </c>
       <c r="D5" t="n">
-        <v>34.38571334124454</v>
+        <v>46.85390918517903</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.72080810356219</v>
+        <v>23.66797365398211</v>
       </c>
       <c r="C6" t="n">
-        <v>108.7599741718702</v>
+        <v>68.83033154474388</v>
       </c>
       <c r="D6" t="n">
-        <v>32.28182801104362</v>
+        <v>35.62271544859552</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.05528097107408</v>
+        <v>11.49822911213864</v>
       </c>
       <c r="C7" t="n">
-        <v>67.97130230352791</v>
+        <v>38.14777054391831</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>30.62561963397925</v>
+        <v>21.44627859927157</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.259515024325998</v>
+        <v>7.270742245372648</v>
       </c>
       <c r="C21" t="n">
-        <v>75.31746837738223</v>
+        <v>75.43395079574123</v>
       </c>
       <c r="D21" t="n">
-        <v>5.444636268244498</v>
+        <v>5.453056684029486</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.904811530417065</v>
+        <v>5.085453107998478</v>
       </c>
       <c r="C2" t="n">
-        <v>9.579894098040375</v>
+        <v>6.776022654711485</v>
       </c>
       <c r="D2" t="n">
-        <v>27.84432838784804</v>
+        <v>23.70626181444773</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.57466656434965</v>
+        <v>22.68818944514379</v>
       </c>
       <c r="C3" t="n">
-        <v>27.93563092434299</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D3" t="n">
-        <v>62.43424525157591</v>
+        <v>74.56864687606648</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.60798923303181</v>
+        <v>38.49236398810894</v>
       </c>
       <c r="C4" t="n">
-        <v>64.03056701868123</v>
+        <v>76.80604989404496</v>
       </c>
       <c r="D4" t="n">
-        <v>67.84662034508857</v>
+        <v>95.38857044002859</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.39262663290327</v>
+        <v>40.6934423410303</v>
       </c>
       <c r="C5" t="n">
-        <v>112.3364810584413</v>
+        <v>113.3182287626881</v>
       </c>
       <c r="D5" t="n">
-        <v>45.01313223971626</v>
+        <v>63.73996969822418</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.38120551335081</v>
+        <v>34.21390749300134</v>
       </c>
       <c r="C6" t="n">
-        <v>139.9147558184385</v>
+        <v>107.2706629045278</v>
       </c>
       <c r="D6" t="n">
-        <v>35.66296710446964</v>
+        <v>41.90197376495812</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.15804568485051</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>115.7608170508541</v>
+        <v>70.48653992180824</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>61.66848204226339</v>
+        <v>37.21805546799658</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>31.50624732468863</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>22.89435646303562</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.461661171328011</v>
+        <v>7.475176673217309</v>
       </c>
       <c r="C21" t="n">
-        <v>83.94368817744012</v>
+        <v>84.09573757369472</v>
       </c>
       <c r="D21" t="n">
-        <v>6.528953524912009</v>
+        <v>6.540779589065145</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_4_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497650699067</v>
+        <v>10.84497641549466</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907255091111</v>
+        <v>37.78907223209535</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.233697011339745</v>
+        <v>0.7107853378746907</v>
       </c>
       <c r="C2" t="n">
-        <v>8.605018627723293</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="D2" t="n">
-        <v>28.55707722113122</v>
+        <v>14.67909167389831</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.77239876353076</v>
+        <v>7.230571841777759</v>
       </c>
       <c r="C3" t="n">
-        <v>24.70568097737099</v>
+        <v>26.67408512438584</v>
       </c>
       <c r="D3" t="n">
-        <v>75.76637907524758</v>
+        <v>68.22655670663208</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.80241633620168</v>
+        <v>12.21392318853457</v>
       </c>
       <c r="C4" t="n">
-        <v>66.44272112801563</v>
+        <v>91.29173727020665</v>
       </c>
       <c r="D4" t="n">
-        <v>109.5041389316892</v>
+        <v>77.31655870025331</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.2837347531899</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C5" t="n">
-        <v>126.6945412330509</v>
+        <v>106.4459948329604</v>
       </c>
       <c r="D5" t="n">
-        <v>80.724204981694</v>
+        <v>47.41841411512095</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.23656980565704</v>
+        <v>8.251589454194443</v>
       </c>
       <c r="C6" t="n">
-        <v>143.8594180941022</v>
+        <v>63.51711296936016</v>
       </c>
       <c r="D6" t="n">
-        <v>51.52211951887262</v>
+        <v>30.59125846433062</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.30262463928205</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>111.6286409636793</v>
+        <v>35.81219275551515</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.60487975900305</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>65.25676990128548</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.664584622964162</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.93308855344046</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.664584622964162</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.041094534858124</v>
+        <v>0.4682936549257286</v>
       </c>
       <c r="C2" t="n">
-        <v>7.789186285494193</v>
+        <v>3.713951565165684</v>
       </c>
       <c r="D2" t="n">
-        <v>28.1771408595877</v>
+        <v>15.04724706299086</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.48140053244621</v>
+        <v>4.653484118129881</v>
       </c>
       <c r="C3" t="n">
-        <v>28.85356502781376</v>
+        <v>15.62942345160922</v>
       </c>
       <c r="D3" t="n">
-        <v>79.37430188835462</v>
+        <v>64.13757751844412</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.7220929509027</v>
+        <v>13.24770352110646</v>
       </c>
       <c r="C4" t="n">
-        <v>63.405193731076</v>
+        <v>77.176168778546</v>
       </c>
       <c r="D4" t="n">
-        <v>118.5529075217321</v>
+        <v>94.17611202528377</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.29064804484862</v>
+        <v>14.67712817848982</v>
       </c>
       <c r="C5" t="n">
-        <v>124.5346962837079</v>
+        <v>142.4025045009999</v>
       </c>
       <c r="D5" t="n">
-        <v>98.19931411728723</v>
+        <v>64.42719309119694</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.50074205355744</v>
+        <v>11.18996033300515</v>
       </c>
       <c r="C6" t="n">
-        <v>168.6946897684337</v>
+        <v>119.9096828490012</v>
       </c>
       <c r="D6" t="n">
-        <v>61.9472983902695</v>
+        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.06414206260808</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>154.6272269142811</v>
+        <v>64.85719858565703</v>
       </c>
       <c r="D7" t="n">
-        <v>44.6155244194963</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.11524969649115</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>103.2258623630309</v>
+        <v>38.38633523605029</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>56.02343274284421</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.838170652770653</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9164471544221</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.817941984366984</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.103345550853172</v>
+        <v>0.2395464398362217</v>
       </c>
       <c r="C2" t="n">
-        <v>7.198174167537614</v>
+        <v>1.498146996680633</v>
       </c>
       <c r="D2" t="n">
-        <v>34.3660783871596</v>
+        <v>10.13850854175681</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.33690369347268</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C3" t="n">
-        <v>29.21681167838507</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D3" t="n">
-        <v>81.67159151629215</v>
+        <v>63.81360077604268</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.25888796094745</v>
+        <v>14.33253473429918</v>
       </c>
       <c r="C4" t="n">
-        <v>66.37890752723959</v>
+        <v>68.24226466990004</v>
       </c>
       <c r="D4" t="n">
-        <v>126.4530312978062</v>
+        <v>104.1948473471225</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.93507544946203</v>
+        <v>14.79984664152067</v>
       </c>
       <c r="C5" t="n">
-        <v>120.8531423927824</v>
+        <v>161.6693031968435</v>
       </c>
       <c r="D5" t="n">
-        <v>113.88273369263</v>
+        <v>74.34284490408973</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.70578845502478</v>
+        <v>10.02266231265569</v>
       </c>
       <c r="C6" t="n">
-        <v>179.5626368544459</v>
+        <v>157.7462393706733</v>
       </c>
       <c r="D6" t="n">
-        <v>73.82153687313468</v>
+        <v>39.00385454202154</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.88554609589318</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>190.7987393295506</v>
+        <v>63.71935299643498</v>
       </c>
       <c r="D7" t="n">
-        <v>50.66407202536089</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.2097595180061</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>146.034971006713</v>
+        <v>40.13875488813084</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.97499864350409</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>84.86718029361549</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>48.11545498513618</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.53926689373453</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.996362343433392</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.9508916363508</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.995452929291741</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.42692138262712</v>
+        <v>0.6342090169434395</v>
       </c>
       <c r="C2" t="n">
-        <v>4.951935420220912</v>
+        <v>10.2808619588726</v>
       </c>
       <c r="D2" t="n">
-        <v>28.27629737771663</v>
+        <v>16.32842781703295</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.52896639060656</v>
+        <v>2.248202242725196</v>
       </c>
       <c r="C3" t="n">
-        <v>42.86310476741574</v>
+        <v>10.13163630782708</v>
       </c>
       <c r="D3" t="n">
-        <v>89.42248964132074</v>
+        <v>57.32424845097125</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.86552592671396</v>
+        <v>10.9121257327033</v>
       </c>
       <c r="C4" t="n">
-        <v>96.0139437276338</v>
+        <v>53.0801531255123</v>
       </c>
       <c r="D4" t="n">
-        <v>123.4793175016426</v>
+        <v>112.2736492053695</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.7538687303371</v>
+        <v>18.45685683984004</v>
       </c>
       <c r="C5" t="n">
-        <v>107.2804803815702</v>
+        <v>144.0714755982195</v>
       </c>
       <c r="D5" t="n">
-        <v>74.71100029318228</v>
+        <v>94.56684761157402</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.95352336719769</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="C6" t="n">
-        <v>125.6656696390002</v>
+        <v>211.7237098978671</v>
       </c>
       <c r="D6" t="n">
-        <v>33.36862271964485</v>
+        <v>51.20010627187966</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>102.645649469821</v>
+        <v>143.667977291774</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>62.50296759087318</v>
+        <v>61.75193059712436</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>36.72030938194344</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.473824288252715</v>
+        <v>0.3239767424014474</v>
       </c>
       <c r="C2" t="n">
-        <v>3.233876937788994</v>
+        <v>4.217588137444298</v>
       </c>
       <c r="D2" t="n">
-        <v>20.53423498202629</v>
+        <v>12.25712008752143</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.67270246605409</v>
+        <v>2.267837196810132</v>
       </c>
       <c r="C3" t="n">
-        <v>31.49446635223768</v>
+        <v>26.6544501703009</v>
       </c>
       <c r="D3" t="n">
-        <v>92.19592690581797</v>
+        <v>57.98201941281663</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.86324363613598</v>
+        <v>8.436158022592842</v>
       </c>
       <c r="C4" t="n">
-        <v>104.8074579145725</v>
+        <v>40.66202641449439</v>
       </c>
       <c r="D4" t="n">
-        <v>136.5993938211969</v>
+        <v>115.5791937255685</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.48451000647497</v>
+        <v>18.99681807717579</v>
       </c>
       <c r="C5" t="n">
-        <v>141.3716694115407</v>
+        <v>128.4616871006952</v>
       </c>
       <c r="D5" t="n">
-        <v>94.1741485298753</v>
+        <v>109.8084807200058</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.95102009244145</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>149.0116300459894</v>
+        <v>229.5149417942279</v>
       </c>
       <c r="D6" t="n">
-        <v>42.82776185006286</v>
+        <v>62.51082157250717</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>133.966346478407</v>
+        <v>208.58506248739</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>41.62119392154352</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>83.94924619014475</v>
+        <v>96.96722074845746</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71249645803847</v>
+        <v>49.25624581747095</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.257258956241669</v>
+        <v>0.4496404485450391</v>
       </c>
       <c r="C2" t="n">
-        <v>7.347399818583129</v>
+        <v>6.813329067472864</v>
       </c>
       <c r="D2" t="n">
-        <v>25.4380647647391</v>
+        <v>14.82635382953533</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.42035224833366</v>
+        <v>1.673879835740812</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71135047941821</v>
+        <v>21.22047662729481</v>
       </c>
       <c r="D3" t="n">
-        <v>87.42463306317848</v>
+        <v>54.46736263161304</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.25736643389546</v>
+        <v>6.419648238069893</v>
       </c>
       <c r="C4" t="n">
-        <v>91.62356799424208</v>
+        <v>54.10117073792898</v>
       </c>
       <c r="D4" t="n">
-        <v>149.272774935319</v>
+        <v>118.1317377566102</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.43037501402116</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="C5" t="n">
-        <v>166.1607989437727</v>
+        <v>101.6599747747572</v>
       </c>
       <c r="D5" t="n">
-        <v>117.1715885018568</v>
+        <v>124.8046769023758</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.59254331167113</v>
+        <v>21.65539086027615</v>
       </c>
       <c r="C6" t="n">
-        <v>185.6003852355638</v>
+        <v>220.780332469544</v>
       </c>
       <c r="D6" t="n">
-        <v>58.32464936159877</v>
+        <v>79.69827863075608</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.04500583014188</v>
+        <v>13.83380690054181</v>
       </c>
       <c r="C7" t="n">
-        <v>170.8564982131851</v>
+        <v>269.1304251559951</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>48.74770050667112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>126.0073178400781</v>
+        <v>177.578524744163</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>42.22496875965531</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>68.44843168779184</v>
+        <v>80.09686819868024</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>43.37655881673681</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.148464887519521</v>
+        <v>0.2984513020910303</v>
       </c>
       <c r="C2" t="n">
-        <v>3.513675033499335</v>
+        <v>3.433171721751096</v>
       </c>
       <c r="D2" t="n">
-        <v>17.73919926803562</v>
+        <v>10.67454278827557</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.02412708644545</v>
+        <v>2.380738182798515</v>
       </c>
       <c r="C3" t="n">
-        <v>26.01140542401924</v>
+        <v>26.58081909248239</v>
       </c>
       <c r="D3" t="n">
-        <v>89.59920422808516</v>
+        <v>59.43991475362314</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.45630136495907</v>
+        <v>11.01422749394496</v>
       </c>
       <c r="C4" t="n">
-        <v>87.36081946240242</v>
+        <v>74.68743834828035</v>
       </c>
       <c r="D4" t="n">
-        <v>159.2149339362265</v>
+        <v>123.9260127070749</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.14843349645307</v>
+        <v>13.57266201121216</v>
       </c>
       <c r="C5" t="n">
-        <v>193.6988220478957</v>
+        <v>169.4987411382118</v>
       </c>
       <c r="D5" t="n">
-        <v>123.4547738090364</v>
+        <v>116.3125592606409</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.34095385747668</v>
+        <v>8.573602701187397</v>
       </c>
       <c r="C6" t="n">
-        <v>221.1828490282852</v>
+        <v>235.6734451429681</v>
       </c>
       <c r="D6" t="n">
-        <v>56.63407981488576</v>
+        <v>67.90454345963914</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.803331663981149</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>173.3118492215064</v>
+        <v>124.8635817646306</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>88.70581381722054</v>
+        <v>58.99812828671206</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.079161711145497</v>
+        <v>0.1786780821729195</v>
       </c>
       <c r="C2" t="n">
-        <v>10.34369381194439</v>
+        <v>2.02240027074843</v>
       </c>
       <c r="D2" t="n">
-        <v>19.93536888243573</v>
+        <v>7.251188543566941</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96321767105314</v>
+        <v>1.68369731278328</v>
       </c>
       <c r="C3" t="n">
-        <v>19.87057353395544</v>
+        <v>19.23243752619501</v>
       </c>
       <c r="D3" t="n">
-        <v>84.31249284071608</v>
+        <v>54.72752577323844</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.87823189360694</v>
+        <v>7.325801369089699</v>
       </c>
       <c r="C4" t="n">
-        <v>76.44869372969913</v>
+        <v>67.51478962105315</v>
       </c>
       <c r="D4" t="n">
-        <v>165.6983957750724</v>
+        <v>120.26311202253</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.69592992025331</v>
+        <v>12.22275891787279</v>
       </c>
       <c r="C5" t="n">
-        <v>180.1752474218959</v>
+        <v>139.2854555400162</v>
       </c>
       <c r="D5" t="n">
-        <v>146.0104273141069</v>
+        <v>119.5277829920492</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.28940425523712</v>
+        <v>8.372344421816802</v>
       </c>
       <c r="C6" t="n">
-        <v>261.1527433112856</v>
+        <v>212.0859748007342</v>
       </c>
       <c r="D6" t="n">
-        <v>75.47185476397357</v>
+        <v>72.73474216453346</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>3.473423377625215</v>
       </c>
       <c r="C7" t="n">
-        <v>237.689954927491</v>
+        <v>161.7537334994087</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>144.2825513546325</v>
+        <v>68.26091787628073</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>58.02030757328223</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.891246989006857</v>
+        <v>0.3877903431774901</v>
       </c>
       <c r="C2" t="n">
-        <v>5.951354583144164</v>
+        <v>3.702170592714722</v>
       </c>
       <c r="D2" t="n">
-        <v>14.10771451002667</v>
+        <v>10.88758204009713</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.20236320026186</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C3" t="n">
-        <v>29.45733986592554</v>
+        <v>12.23748513343649</v>
       </c>
       <c r="D3" t="n">
-        <v>82.37844986334986</v>
+        <v>47.8307481509046</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.41127983928396</v>
+        <v>5.194427103169875</v>
       </c>
       <c r="C4" t="n">
-        <v>66.57034832956771</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D4" t="n">
-        <v>168.9273639743402</v>
+        <v>120.8246717093592</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.89919275276141</v>
+        <v>11.95277829920492</v>
       </c>
       <c r="C5" t="n">
-        <v>171.5604113171301</v>
+        <v>131.2105806725862</v>
       </c>
       <c r="D5" t="n">
-        <v>161.2029730373263</v>
+        <v>136.2665813494573</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.13847715069036</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="C6" t="n">
-        <v>282.4056176128205</v>
+        <v>220.3375642549287</v>
       </c>
       <c r="D6" t="n">
-        <v>90.92849061963534</v>
+        <v>93.02157672508955</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>289.3720993221558</v>
+        <v>241.6424711847887</v>
       </c>
       <c r="D7" t="n">
-        <v>46.11268966847268</v>
+        <v>47.9691745772034</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>186.5075201142878</v>
+        <v>144.2825513546325</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>66.67343183851361</v>
+        <v>58.46405753560178</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>18.12502611580461</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.806235849364884</v>
+        <v>0.1060287520586555</v>
       </c>
       <c r="C2" t="n">
-        <v>6.555129421255953</v>
+        <v>9.04582334693011</v>
       </c>
       <c r="D2" t="n">
-        <v>18.01114338211198</v>
+        <v>18.29094147782232</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.58109682992288</v>
+        <v>1.217367153266045</v>
       </c>
       <c r="C3" t="n">
-        <v>26.59063656952486</v>
+        <v>13.43030859409637</v>
       </c>
       <c r="D3" t="n">
-        <v>75.68293052038661</v>
+        <v>45.46473618366979</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.28066633689012</v>
+        <v>3.548036203147973</v>
       </c>
       <c r="C4" t="n">
-        <v>69.31433316293754</v>
+        <v>42.35946819513713</v>
       </c>
       <c r="D4" t="n">
-        <v>170.3057377511027</v>
+        <v>117.7871443124196</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.33468782281949</v>
+        <v>10.13654504634832</v>
       </c>
       <c r="C5" t="n">
-        <v>150.8455347575224</v>
+        <v>117.1470448092507</v>
       </c>
       <c r="D5" t="n">
-        <v>178.2853830912208</v>
+        <v>148.7102335007856</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.12088780747193</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="C6" t="n">
-        <v>279.6685050133804</v>
+        <v>215.4671138941602</v>
       </c>
       <c r="D6" t="n">
-        <v>111.3763318036879</v>
+        <v>112.1008616094221</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.75797564760332</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>336.6226345798506</v>
+        <v>282.9043454465778</v>
       </c>
       <c r="D7" t="n">
-        <v>56.11375353163493</v>
+        <v>62.52162079725387</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>262.5291535926395</v>
+        <v>232.8214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>123.473427015417</v>
+        <v>117.1499900523633</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>47.97310156802039</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.23606141737574</v>
+        <v>2.471058971589222</v>
       </c>
       <c r="C2" t="n">
-        <v>4.185190463204153</v>
+        <v>5.892449720889356</v>
       </c>
       <c r="D2" t="n">
-        <v>9.447358157967058</v>
+        <v>9.171487053073703</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.752820562708056</v>
+        <v>0.4928373475318988</v>
       </c>
       <c r="C2" t="n">
-        <v>3.774819922828986</v>
+        <v>13.1878169111474</v>
       </c>
       <c r="D2" t="n">
-        <v>13.39987441526472</v>
+        <v>18.85740990317273</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50808764691012</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="C3" t="n">
-        <v>30.31146036862027</v>
+        <v>24.53387512912779</v>
       </c>
       <c r="D3" t="n">
-        <v>82.09865176763952</v>
+        <v>48.66032496099316</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.97957289132261</v>
+        <v>2.909900195387546</v>
       </c>
       <c r="C4" t="n">
-        <v>98.01769079200155</v>
+        <v>37.90527886096935</v>
       </c>
       <c r="D4" t="n">
-        <v>174.2877064395278</v>
+        <v>114.264633549582</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.25732537616646</v>
+        <v>8.123962252642357</v>
       </c>
       <c r="C5" t="n">
-        <v>232.3796815952201</v>
+        <v>97.11939164261574</v>
       </c>
       <c r="D5" t="n">
-        <v>161.6202158116312</v>
+        <v>154.6988944966912</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.32708621643021</v>
+        <v>14.28933783531233</v>
       </c>
       <c r="C6" t="n">
-        <v>273.791763255759</v>
+        <v>202.7878422938127</v>
       </c>
       <c r="D6" t="n">
-        <v>86.70206675285282</v>
+        <v>130.8178815908875</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>13.77392029058275</v>
       </c>
       <c r="C7" t="n">
-        <v>184.6304185037679</v>
+        <v>299.3731631853181</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>76.59497413763189</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>90.95892479846698</v>
+        <v>300.6651431641069</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>43.30979997284804</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>193.1421710995877</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>87.97441177755668</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.91890015564179</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>37.84931924182727</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.563965150594174</v>
+        <v>2.80387144332889</v>
       </c>
       <c r="C2" t="n">
-        <v>9.026188392845174</v>
+        <v>8.160286917699487</v>
       </c>
       <c r="D2" t="n">
-        <v>26.77716863333175</v>
+        <v>18.59135627532185</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.24377653028947</v>
+        <v>4.0938879267092</v>
       </c>
       <c r="C3" t="n">
-        <v>10.54397034361075</v>
+        <v>11.6337102953247</v>
       </c>
       <c r="D3" t="n">
-        <v>11.06920536538279</v>
+        <v>9.297150759217294</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39859138514819</v>
+        <v>11.67868187817532</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14556666342288</v>
+        <v>59.95056697463333</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576304868840964</v>
+        <v>0.778578791878355</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.614615120587509</v>
+        <v>1.673879835740812</v>
       </c>
       <c r="C2" t="n">
-        <v>5.62345084992573</v>
+        <v>6.038730128822131</v>
       </c>
       <c r="D2" t="n">
-        <v>25.81211064005714</v>
+        <v>18.16527777167873</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.91827826083604</v>
+        <v>7.65763209312512</v>
       </c>
       <c r="C3" t="n">
-        <v>25.96722677732814</v>
+        <v>25.12292375167588</v>
       </c>
       <c r="D3" t="n">
-        <v>30.88578277560466</v>
+        <v>23.32141671438298</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.39184050718149</v>
+        <v>5.271003424101125</v>
       </c>
       <c r="C4" t="n">
-        <v>16.61706164208151</v>
+        <v>19.47591095684822</v>
       </c>
       <c r="D4" t="n">
-        <v>20.86704745376596</v>
+        <v>19.09302935219197</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44018670261402</v>
+        <v>13.6315759800296</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13998897247821</v>
+        <v>73.77088177427784</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250565621602951</v>
+        <v>1.603714821179953</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.221335201812037</v>
+        <v>1.352848336452105</v>
       </c>
       <c r="C2" t="n">
-        <v>10.9877203059303</v>
+        <v>4.777184328864979</v>
       </c>
       <c r="D2" t="n">
-        <v>31.7340127920739</v>
+        <v>22.57430671145116</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.22262004915255</v>
+        <v>6.612070788102269</v>
       </c>
       <c r="C3" t="n">
-        <v>23.48831382410494</v>
+        <v>24.14117604742907</v>
       </c>
       <c r="D3" t="n">
-        <v>44.36517875491336</v>
+        <v>32.94254421600172</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.47813649416398</v>
+        <v>11.01422749394496</v>
       </c>
       <c r="C4" t="n">
-        <v>45.09069030835175</v>
+        <v>46.78813208899449</v>
       </c>
       <c r="D4" t="n">
-        <v>31.63878326476196</v>
+        <v>26.69961056469625</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.35176877775663</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="C5" t="n">
-        <v>19.8067599331794</v>
+        <v>23.90555659840983</v>
       </c>
       <c r="D5" t="n">
-        <v>30.16419821298325</v>
+        <v>26.97351817418112</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73166530651699</v>
+        <v>14.8463139896331</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0631583697536</v>
+        <v>87.42829349450605</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182916326629248</v>
+        <v>2.47438566493885</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.698063675448488</v>
+        <v>2.119593293468863</v>
       </c>
       <c r="C2" t="n">
-        <v>8.630544068033711</v>
+        <v>6.598326320242812</v>
       </c>
       <c r="D2" t="n">
-        <v>30.1003846122072</v>
+        <v>23.64441170908018</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.28781630826034</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="C3" t="n">
-        <v>34.53297549688155</v>
+        <v>20.73451151369264</v>
       </c>
       <c r="D3" t="n">
-        <v>58.61524668205582</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.45559735469531</v>
+        <v>12.20116046837936</v>
       </c>
       <c r="C4" t="n">
-        <v>52.73555968132166</v>
+        <v>55.00732386894879</v>
       </c>
       <c r="D4" t="n">
-        <v>45.94579255875072</v>
+        <v>36.94807484932871</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.26804248545517</v>
+        <v>11.36372967665683</v>
       </c>
       <c r="C5" t="n">
-        <v>54.0697548113931</v>
+        <v>60.18113427032949</v>
       </c>
       <c r="D5" t="n">
-        <v>34.23845118560752</v>
+        <v>30.82687791334985</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.87423848286517</v>
+        <v>6.198755004614362</v>
       </c>
       <c r="C6" t="n">
-        <v>22.05790741901734</v>
+        <v>25.76105975943631</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05221403152856</v>
+        <v>16.09587579020463</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7692058247339</v>
+        <v>101.6581628855029</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017404677176185</v>
+        <v>3.388605429516765</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.456373813754525</v>
+        <v>2.154936210821749</v>
       </c>
       <c r="C2" t="n">
-        <v>8.241771977151974</v>
+        <v>6.563965150594174</v>
       </c>
       <c r="D2" t="n">
-        <v>27.25822500841269</v>
+        <v>26.38643304704152</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.8039946165159</v>
+        <v>6.513896017677587</v>
       </c>
       <c r="C3" t="n">
-        <v>31.84789552576653</v>
+        <v>23.60121481009332</v>
       </c>
       <c r="D3" t="n">
-        <v>64.40264939859075</v>
+        <v>51.68410789007334</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.06147455693583</v>
+        <v>11.47368541953247</v>
       </c>
       <c r="C4" t="n">
-        <v>59.15520791939156</v>
+        <v>53.25883120768522</v>
       </c>
       <c r="D4" t="n">
-        <v>55.83690067903733</v>
+        <v>49.28962523941536</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.12015843501239</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C5" t="n">
-        <v>57.43224069843842</v>
+        <v>82.41771977151974</v>
       </c>
       <c r="D5" t="n">
-        <v>34.18936380039518</v>
+        <v>37.20823799095412</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.32329809433347</v>
+        <v>10.98870205363455</v>
       </c>
       <c r="C6" t="n">
-        <v>36.8302651248191</v>
+        <v>63.27560303411543</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>35.94472869558847</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>17.18745705824891</v>
+        <v>28.086820070797</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052547678293223</v>
+        <v>17.37435879354716</v>
       </c>
       <c r="C21" t="n">
-        <v>66.11763448399896</v>
+        <v>115.5394859770886</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407842298933264</v>
+        <v>4.34358969838679</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.560038159777187</v>
+        <v>1.598285262513807</v>
       </c>
       <c r="C2" t="n">
-        <v>4.309872421643497</v>
+        <v>7.40237769002095</v>
       </c>
       <c r="D2" t="n">
-        <v>24.34439782220816</v>
+        <v>26.69273833076653</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.78636421556847</v>
+        <v>6.931138791982481</v>
       </c>
       <c r="C3" t="n">
-        <v>32.05406254365836</v>
+        <v>24.59768872990384</v>
       </c>
       <c r="D3" t="n">
-        <v>71.73630474931444</v>
+        <v>59.6804429411636</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.60049510429634</v>
+        <v>11.9586687854304</v>
       </c>
       <c r="C4" t="n">
-        <v>71.99450439553134</v>
+        <v>56.34740948524568</v>
       </c>
       <c r="D4" t="n">
-        <v>76.62737181187205</v>
+        <v>62.01405723415827</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.22586839190156</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C5" t="n">
-        <v>88.11185645615124</v>
+        <v>89.8790023237955</v>
       </c>
       <c r="D5" t="n">
-        <v>46.85390918517903</v>
+        <v>46.01942363656924</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.66797365398211</v>
+        <v>15.49688751153591</v>
       </c>
       <c r="C6" t="n">
-        <v>68.83033154474388</v>
+        <v>97.77127211823561</v>
       </c>
       <c r="D6" t="n">
-        <v>35.62271544859552</v>
+        <v>39.16486116551801</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>38.14777054391831</v>
+        <v>59.76683673913732</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>21.44627859927157</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.270742245372648</v>
+        <v>18.67547466878437</v>
       </c>
       <c r="C21" t="n">
-        <v>75.43395079574123</v>
+        <v>128.9497060463683</v>
       </c>
       <c r="D21" t="n">
-        <v>5.453056684029486</v>
+        <v>5.335849905366964</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.085453107998478</v>
+        <v>1.490293015046658</v>
       </c>
       <c r="C2" t="n">
-        <v>6.776022654711485</v>
+        <v>4.500331476267379</v>
       </c>
       <c r="D2" t="n">
-        <v>23.70626181444773</v>
+        <v>20.82777754559608</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.68818944514379</v>
+        <v>8.757189521881548</v>
       </c>
       <c r="C3" t="n">
-        <v>22.91890015564179</v>
+        <v>37.5813021185679</v>
       </c>
       <c r="D3" t="n">
-        <v>74.56864687606648</v>
+        <v>66.56249434793374</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.49236398810894</v>
+        <v>7.810784734987624</v>
       </c>
       <c r="C4" t="n">
-        <v>76.80604989404496</v>
+        <v>81.10708658635023</v>
       </c>
       <c r="D4" t="n">
-        <v>95.38857044002859</v>
+        <v>58.10866486666446</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.6934423410303</v>
+        <v>8.713010875190443</v>
       </c>
       <c r="C5" t="n">
-        <v>113.3182287626881</v>
+        <v>58.41398840268523</v>
       </c>
       <c r="D5" t="n">
-        <v>63.73996969822418</v>
+        <v>37.08551952792327</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.21390749300134</v>
+        <v>6.31950997223672</v>
       </c>
       <c r="C6" t="n">
-        <v>107.2706629045278</v>
+        <v>39.36611944488861</v>
       </c>
       <c r="D6" t="n">
-        <v>41.90197376495812</v>
+        <v>25.88181472705867</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>70.48653992180824</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>27.66761380108361</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>37.21805546799658</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.475176673217309</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.09573757369472</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.540779589065145</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
